--- a/outputs/capt_fv_report.xlsx
+++ b/outputs/capt_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.74</v>
+        <v>12.79</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/capt_fv_report.xlsx
+++ b/outputs/capt_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16.71143322016474</v>
+        <v>16.71020873669256</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17.74274275688312</v>
+        <v>17.74410951536136</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14.3050443011552</v>
+        <v>14.29777358646538</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.499555247383149</v>
+        <v>2.499534431147925</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.412766030243104e-24</v>
+        <v>2.412725919828292e-24</v>
       </c>
     </row>
     <row r="16">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>290.3454489250489</v>
+        <v>290.528184533589</v>
       </c>
     </row>
     <row r="5">
@@ -733,7 +733,7 @@
         <v/>
       </c>
       <c r="B12" t="n">
-        <v>2372.204706595273</v>
+        <v>2372.387442203813</v>
       </c>
     </row>
     <row r="13">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17.74274275688312</v>
+        <v>17.74410951536136</v>
       </c>
     </row>
     <row r="15">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17.74274275688312</v>
+        <v>17.74410951536136</v>
       </c>
     </row>
     <row r="16">
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>13.94566319128148</v>
+        <v>13.93646814742258</v>
       </c>
       <c r="F11" t="n">
-        <v>11.02712937318321</v>
+        <v>11.01985865849339</v>
       </c>
     </row>
     <row r="12">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>14.3050443011552</v>
+        <v>14.29777358646538</v>
       </c>
     </row>
     <row r="13">
@@ -1110,19 +1110,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.85549434766949</v>
+        <v>10.85451476089174</v>
       </c>
       <c r="C2" t="n">
-        <v>13.60525324384789</v>
+        <v>13.60415120872292</v>
       </c>
       <c r="D2" t="n">
-        <v>16.35501214002628</v>
+        <v>16.3537876565541</v>
       </c>
       <c r="E2" t="n">
-        <v>19.10477103620468</v>
+        <v>19.10342410438528</v>
       </c>
       <c r="F2" t="n">
-        <v>21.85452993238307</v>
+        <v>21.85306055221645</v>
       </c>
     </row>
     <row r="3">
@@ -1132,19 +1132,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11.03370488773872</v>
+        <v>11.03272530096098</v>
       </c>
       <c r="C3" t="n">
-        <v>13.78346378391712</v>
+        <v>13.78236174879215</v>
       </c>
       <c r="D3" t="n">
-        <v>16.53322268009551</v>
+        <v>16.53199819662333</v>
       </c>
       <c r="E3" t="n">
-        <v>19.28298157627391</v>
+        <v>19.28163464445451</v>
       </c>
       <c r="F3" t="n">
-        <v>22.0327404724523</v>
+        <v>22.03127109228568</v>
       </c>
     </row>
     <row r="4">
@@ -1154,19 +1154,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11.21191542780795</v>
+        <v>11.21093584103021</v>
       </c>
       <c r="C4" t="n">
-        <v>13.96167432398635</v>
+        <v>13.96057228886139</v>
       </c>
       <c r="D4" t="n">
-        <v>16.71143322016474</v>
+        <v>16.71020873669256</v>
       </c>
       <c r="E4" t="n">
-        <v>19.46119211634314</v>
+        <v>19.45984518452374</v>
       </c>
       <c r="F4" t="n">
-        <v>22.21095101252153</v>
+        <v>22.20948163235491</v>
       </c>
     </row>
     <row r="5">
@@ -1176,19 +1176,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.39012596787719</v>
+        <v>11.38914638109944</v>
       </c>
       <c r="C5" t="n">
-        <v>14.13988486405558</v>
+        <v>14.13878282893062</v>
       </c>
       <c r="D5" t="n">
-        <v>16.88964376023397</v>
+        <v>16.88841927676179</v>
       </c>
       <c r="E5" t="n">
-        <v>19.63940265641238</v>
+        <v>19.63805572459297</v>
       </c>
       <c r="F5" t="n">
-        <v>22.38916155259076</v>
+        <v>22.38769217242414</v>
       </c>
     </row>
     <row r="6">
@@ -1198,19 +1198,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.56833650794642</v>
+        <v>11.56735692116867</v>
       </c>
       <c r="C6" t="n">
-        <v>14.31809540412481</v>
+        <v>14.31699336899985</v>
       </c>
       <c r="D6" t="n">
-        <v>17.06785430030321</v>
+        <v>17.06662981683102</v>
       </c>
       <c r="E6" t="n">
-        <v>19.81761319648161</v>
+        <v>19.8162662646622</v>
       </c>
       <c r="F6" t="n">
-        <v>22.56737209265999</v>
+        <v>22.56590271249337</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/capt_fv_report.xlsx
+++ b/outputs/capt_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.79</v>
+        <v>13.24</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16.71020873669256</v>
+        <v>15.24488700748108</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17.74410951536136</v>
+        <v>15.04601435900841</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14.29777358646538</v>
+        <v>15.70892318725065</v>
       </c>
     </row>
     <row r="9">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.412725919828292e-24</v>
+        <v>2.377308841647097e-24</v>
       </c>
     </row>
     <row r="16">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2235</v>
+        <v>1947.890654266113</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1149</v>
+        <v>1075.374023329498</v>
       </c>
     </row>
     <row r="4">
@@ -733,7 +733,7 @@
         <v/>
       </c>
       <c r="B12" t="n">
-        <v>2372.387442203813</v>
+        <v>2011.652119799425</v>
       </c>
     </row>
     <row r="13">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17.74410951536136</v>
+        <v>15.04601435900841</v>
       </c>
     </row>
     <row r="15">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17.74410951536136</v>
+        <v>15.04601435900841</v>
       </c>
     </row>
     <row r="16">
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>13.93646814742258</v>
+        <v>15.72110459985425</v>
       </c>
       <c r="F11" t="n">
-        <v>11.01985865849339</v>
+        <v>12.43100825927867</v>
       </c>
     </row>
     <row r="12">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>14.29777358646538</v>
+        <v>15.70892318725065</v>
       </c>
     </row>
     <row r="13">
@@ -1110,19 +1110,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.85451476089174</v>
+        <v>9.682257377522564</v>
       </c>
       <c r="C2" t="n">
-        <v>13.60415120872292</v>
+        <v>12.28536165243259</v>
       </c>
       <c r="D2" t="n">
-        <v>16.3537876565541</v>
+        <v>14.88846592734262</v>
       </c>
       <c r="E2" t="n">
-        <v>19.10342410438528</v>
+        <v>17.49157020225265</v>
       </c>
       <c r="F2" t="n">
-        <v>21.85306055221645</v>
+        <v>20.09467447716268</v>
       </c>
     </row>
     <row r="3">
@@ -1132,19 +1132,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11.03272530096098</v>
+        <v>9.860467917591796</v>
       </c>
       <c r="C3" t="n">
-        <v>13.78236174879215</v>
+        <v>12.46357219250183</v>
       </c>
       <c r="D3" t="n">
-        <v>16.53199819662333</v>
+        <v>15.06667646741185</v>
       </c>
       <c r="E3" t="n">
-        <v>19.28163464445451</v>
+        <v>17.66978074232188</v>
       </c>
       <c r="F3" t="n">
-        <v>22.03127109228568</v>
+        <v>20.27288501723191</v>
       </c>
     </row>
     <row r="4">
@@ -1154,19 +1154,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11.21093584103021</v>
+        <v>10.03867845766103</v>
       </c>
       <c r="C4" t="n">
-        <v>13.96057228886139</v>
+        <v>12.64178273257106</v>
       </c>
       <c r="D4" t="n">
-        <v>16.71020873669256</v>
+        <v>15.24488700748108</v>
       </c>
       <c r="E4" t="n">
-        <v>19.45984518452374</v>
+        <v>17.84799128239111</v>
       </c>
       <c r="F4" t="n">
-        <v>22.20948163235491</v>
+        <v>20.45109555730114</v>
       </c>
     </row>
     <row r="5">
@@ -1176,19 +1176,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.38914638109944</v>
+        <v>10.21688899773026</v>
       </c>
       <c r="C5" t="n">
-        <v>14.13878282893062</v>
+        <v>12.81999327264029</v>
       </c>
       <c r="D5" t="n">
-        <v>16.88841927676179</v>
+        <v>15.42309754755032</v>
       </c>
       <c r="E5" t="n">
-        <v>19.63805572459297</v>
+        <v>18.02620182246034</v>
       </c>
       <c r="F5" t="n">
-        <v>22.38769217242414</v>
+        <v>20.62930609737037</v>
       </c>
     </row>
     <row r="6">
@@ -1198,19 +1198,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.56735692116867</v>
+        <v>10.39509953779949</v>
       </c>
       <c r="C6" t="n">
-        <v>14.31699336899985</v>
+        <v>12.99820381270952</v>
       </c>
       <c r="D6" t="n">
-        <v>17.06662981683102</v>
+        <v>15.60130808761955</v>
       </c>
       <c r="E6" t="n">
-        <v>19.8162662646622</v>
+        <v>18.20441236252958</v>
       </c>
       <c r="F6" t="n">
-        <v>22.56590271249337</v>
+        <v>20.8075166374396</v>
       </c>
     </row>
   </sheetData>
@@ -1248,7 +1248,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>17.48</v>
+        <v>16.01</v>
       </c>
     </row>
     <row r="3">
@@ -1256,7 +1256,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>17.8</v>
+        <v>16.34</v>
       </c>
     </row>
     <row r="4">
@@ -1264,7 +1264,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>17.91</v>
+        <v>16.45</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/capt_fv_report.xlsx
+++ b/outputs/capt_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.24488700748108</v>
+        <v>15.24725560222427</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.04601435900841</v>
+        <v>15.03377777647967</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15.70892318725065</v>
+        <v>15.74537052896167</v>
       </c>
     </row>
     <row r="9">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.377308841647097e-24</v>
+        <v>2.372874560801657e-24</v>
       </c>
     </row>
     <row r="16">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1947.890654266113</v>
+        <v>1935.210557192253</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1075.374023329498</v>
+        <v>1086.418089319266</v>
       </c>
     </row>
     <row r="4">
@@ -733,7 +733,7 @@
         <v/>
       </c>
       <c r="B12" t="n">
-        <v>2011.652119799425</v>
+        <v>2010.016088715332</v>
       </c>
     </row>
     <row r="13">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15.04601435900841</v>
+        <v>15.03377777647967</v>
       </c>
     </row>
     <row r="15">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15.04601435900841</v>
+        <v>15.03377777647967</v>
       </c>
     </row>
     <row r="16">
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>15.72110459985425</v>
+        <v>15.76719840491611</v>
       </c>
       <c r="F11" t="n">
-        <v>12.43100825927867</v>
+        <v>12.46745560098969</v>
       </c>
     </row>
     <row r="12">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>15.70892318725065</v>
+        <v>15.74537052896167</v>
       </c>
     </row>
     <row r="13">
@@ -1110,19 +1110,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.682257377522564</v>
+        <v>9.68415225331711</v>
       </c>
       <c r="C2" t="n">
-        <v>12.28536165243259</v>
+        <v>12.28749338770146</v>
       </c>
       <c r="D2" t="n">
-        <v>14.88846592734262</v>
+        <v>14.89083452208581</v>
       </c>
       <c r="E2" t="n">
-        <v>17.49157020225265</v>
+        <v>17.49417565647016</v>
       </c>
       <c r="F2" t="n">
-        <v>20.09467447716268</v>
+        <v>20.09751679085451</v>
       </c>
     </row>
     <row r="3">
@@ -1132,19 +1132,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.860467917591796</v>
+        <v>9.862362793386342</v>
       </c>
       <c r="C3" t="n">
-        <v>12.46357219250183</v>
+        <v>12.46570392777069</v>
       </c>
       <c r="D3" t="n">
-        <v>15.06667646741185</v>
+        <v>15.06904506215504</v>
       </c>
       <c r="E3" t="n">
-        <v>17.66978074232188</v>
+        <v>17.67238619653939</v>
       </c>
       <c r="F3" t="n">
-        <v>20.27288501723191</v>
+        <v>20.27572733092374</v>
       </c>
     </row>
     <row r="4">
@@ -1154,19 +1154,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.03867845766103</v>
+        <v>10.04057333345557</v>
       </c>
       <c r="C4" t="n">
-        <v>12.64178273257106</v>
+        <v>12.64391446783992</v>
       </c>
       <c r="D4" t="n">
-        <v>15.24488700748108</v>
+        <v>15.24725560222427</v>
       </c>
       <c r="E4" t="n">
-        <v>17.84799128239111</v>
+        <v>17.85059673660862</v>
       </c>
       <c r="F4" t="n">
-        <v>20.45109555730114</v>
+        <v>20.45393787099297</v>
       </c>
     </row>
     <row r="5">
@@ -1176,19 +1176,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.21688899773026</v>
+        <v>10.2187838735248</v>
       </c>
       <c r="C5" t="n">
-        <v>12.81999327264029</v>
+        <v>12.82212500790915</v>
       </c>
       <c r="D5" t="n">
-        <v>15.42309754755032</v>
+        <v>15.4254661422935</v>
       </c>
       <c r="E5" t="n">
-        <v>18.02620182246034</v>
+        <v>18.02880727667785</v>
       </c>
       <c r="F5" t="n">
-        <v>20.62930609737037</v>
+        <v>20.6321484110622</v>
       </c>
     </row>
     <row r="6">
@@ -1198,19 +1198,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.39509953779949</v>
+        <v>10.39699441359403</v>
       </c>
       <c r="C6" t="n">
-        <v>12.99820381270952</v>
+        <v>13.00033554797838</v>
       </c>
       <c r="D6" t="n">
-        <v>15.60130808761955</v>
+        <v>15.60367668236273</v>
       </c>
       <c r="E6" t="n">
-        <v>18.20441236252958</v>
+        <v>18.20701781674709</v>
       </c>
       <c r="F6" t="n">
-        <v>20.8075166374396</v>
+        <v>20.81035895113143</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/capt_fv_report.xlsx
+++ b/outputs/capt_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.24725560222427</v>
+        <v>15.65339743708715</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15.74537052896167</v>
+        <v>17.09917664517126</v>
       </c>
     </row>
     <row r="9">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.372874560801657e-24</v>
+        <v>2790.518946050923</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.97215226305253e-29</v>
+        <v>0.02319266406010958</v>
       </c>
     </row>
   </sheetData>
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>15.76719840491611</v>
+        <v>17.47931435858119</v>
       </c>
       <c r="F11" t="n">
-        <v>12.46745560098969</v>
+        <v>13.82126171719927</v>
       </c>
     </row>
     <row r="12">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>15.74537052896167</v>
+        <v>17.09917664517126</v>
       </c>
     </row>
     <row r="13">
@@ -1110,19 +1110,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.68415225331711</v>
+        <v>9.834187453492572</v>
       </c>
       <c r="C2" t="n">
-        <v>12.28749338770146</v>
+        <v>12.37033667803615</v>
       </c>
       <c r="D2" t="n">
-        <v>14.89083452208581</v>
+        <v>14.90648590257972</v>
       </c>
       <c r="E2" t="n">
-        <v>17.49417565647016</v>
+        <v>17.4426351271233</v>
       </c>
       <c r="F2" t="n">
-        <v>20.09751679085451</v>
+        <v>19.97878435166687</v>
       </c>
     </row>
     <row r="3">
@@ -1132,19 +1132,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.862362793386342</v>
+        <v>10.20764322074628</v>
       </c>
       <c r="C3" t="n">
-        <v>12.46570392777069</v>
+        <v>12.74379244528986</v>
       </c>
       <c r="D3" t="n">
-        <v>15.06904506215504</v>
+        <v>15.27994166983343</v>
       </c>
       <c r="E3" t="n">
-        <v>17.67238619653939</v>
+        <v>17.81609089437702</v>
       </c>
       <c r="F3" t="n">
-        <v>20.27572733092374</v>
+        <v>20.35224011892058</v>
       </c>
     </row>
     <row r="4">
@@ -1154,19 +1154,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.04057333345557</v>
+        <v>10.581098988</v>
       </c>
       <c r="C4" t="n">
-        <v>12.64391446783992</v>
+        <v>13.11724821254357</v>
       </c>
       <c r="D4" t="n">
-        <v>15.24725560222427</v>
+        <v>15.65339743708715</v>
       </c>
       <c r="E4" t="n">
-        <v>17.85059673660862</v>
+        <v>18.18954666163073</v>
       </c>
       <c r="F4" t="n">
-        <v>20.45393787099297</v>
+        <v>20.7256958861743</v>
       </c>
     </row>
     <row r="5">
@@ -1176,19 +1176,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.2187838735248</v>
+        <v>10.95455475525371</v>
       </c>
       <c r="C5" t="n">
-        <v>12.82212500790915</v>
+        <v>13.49070397979728</v>
       </c>
       <c r="D5" t="n">
-        <v>15.4254661422935</v>
+        <v>16.02685320434086</v>
       </c>
       <c r="E5" t="n">
-        <v>18.02880727667785</v>
+        <v>18.56300242888444</v>
       </c>
       <c r="F5" t="n">
-        <v>20.6321484110622</v>
+        <v>21.09915165342801</v>
       </c>
     </row>
     <row r="6">
@@ -1198,19 +1198,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.39699441359403</v>
+        <v>11.32801052250742</v>
       </c>
       <c r="C6" t="n">
-        <v>13.00033554797838</v>
+        <v>13.864159747051</v>
       </c>
       <c r="D6" t="n">
-        <v>15.60367668236273</v>
+        <v>16.40030897159457</v>
       </c>
       <c r="E6" t="n">
-        <v>18.20701781674709</v>
+        <v>18.93645819613815</v>
       </c>
       <c r="F6" t="n">
-        <v>20.81035895113143</v>
+        <v>21.47260742068172</v>
       </c>
     </row>
   </sheetData>
@@ -1248,7 +1248,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>16.01</v>
+        <v>15.73</v>
       </c>
     </row>
     <row r="3">
@@ -1256,7 +1256,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>16.34</v>
+        <v>15.77</v>
       </c>
     </row>
     <row r="4">
@@ -1264,7 +1264,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>16.45</v>
+        <v>15.78</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/capt_fv_report.xlsx
+++ b/outputs/capt_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.65339743708715</v>
+        <v>15.65516714288702</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17.09917664517126</v>
+        <v>17.10507566450418</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.499534431147925</v>
+        <v>2.463949424090978</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2790.518946050923</v>
+        <v>2700.636595187087</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02319266406010958</v>
+        <v>0.02244563054812861</v>
       </c>
     </row>
   </sheetData>
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>17.47931435858119</v>
+        <v>17.48677466252718</v>
       </c>
       <c r="F11" t="n">
-        <v>13.82126171719927</v>
+        <v>13.82716073653219</v>
       </c>
     </row>
     <row r="12">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>17.09917664517126</v>
+        <v>17.10507566450418</v>
       </c>
     </row>
     <row r="13">
@@ -1110,19 +1110,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.834187453492572</v>
+        <v>9.835603218132473</v>
       </c>
       <c r="C2" t="n">
-        <v>12.37033667803615</v>
+        <v>12.37192941325604</v>
       </c>
       <c r="D2" t="n">
-        <v>14.90648590257972</v>
+        <v>14.9082556083796</v>
       </c>
       <c r="E2" t="n">
-        <v>17.4426351271233</v>
+        <v>17.44458180350316</v>
       </c>
       <c r="F2" t="n">
-        <v>19.97878435166687</v>
+        <v>19.98090799862672</v>
       </c>
     </row>
     <row r="3">
@@ -1132,19 +1132,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10.20764322074628</v>
+        <v>10.20905898538619</v>
       </c>
       <c r="C3" t="n">
-        <v>12.74379244528986</v>
+        <v>12.74538518050975</v>
       </c>
       <c r="D3" t="n">
-        <v>15.27994166983343</v>
+        <v>15.28171137563331</v>
       </c>
       <c r="E3" t="n">
-        <v>17.81609089437702</v>
+        <v>17.81803757075687</v>
       </c>
       <c r="F3" t="n">
-        <v>20.35224011892058</v>
+        <v>20.35436376588043</v>
       </c>
     </row>
     <row r="4">
@@ -1154,19 +1154,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.581098988</v>
+        <v>10.5825147526399</v>
       </c>
       <c r="C4" t="n">
-        <v>13.11724821254357</v>
+        <v>13.11884094776346</v>
       </c>
       <c r="D4" t="n">
-        <v>15.65339743708715</v>
+        <v>15.65516714288702</v>
       </c>
       <c r="E4" t="n">
-        <v>18.18954666163073</v>
+        <v>18.19149333801059</v>
       </c>
       <c r="F4" t="n">
-        <v>20.7256958861743</v>
+        <v>20.72781953313415</v>
       </c>
     </row>
     <row r="5">
@@ -1176,19 +1176,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.95455475525371</v>
+        <v>10.95597051989361</v>
       </c>
       <c r="C5" t="n">
-        <v>13.49070397979728</v>
+        <v>13.49229671501717</v>
       </c>
       <c r="D5" t="n">
-        <v>16.02685320434086</v>
+        <v>16.02862291014073</v>
       </c>
       <c r="E5" t="n">
-        <v>18.56300242888444</v>
+        <v>18.5649491052643</v>
       </c>
       <c r="F5" t="n">
-        <v>21.09915165342801</v>
+        <v>21.10127530038786</v>
       </c>
     </row>
     <row r="6">
@@ -1198,19 +1198,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.32801052250742</v>
+        <v>11.32942628714732</v>
       </c>
       <c r="C6" t="n">
-        <v>13.864159747051</v>
+        <v>13.86575248227089</v>
       </c>
       <c r="D6" t="n">
-        <v>16.40030897159457</v>
+        <v>16.40207867739445</v>
       </c>
       <c r="E6" t="n">
-        <v>18.93645819613815</v>
+        <v>18.93840487251801</v>
       </c>
       <c r="F6" t="n">
-        <v>21.47260742068172</v>
+        <v>21.47473106764157</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/capt_fv_report.xlsx
+++ b/outputs/capt_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2700.636595187087</v>
+        <v>2700.636595187088</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/capt_fv_report.xlsx
+++ b/outputs/capt_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13.24</v>
+        <v>12.79</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2700.636595187088</v>
+        <v>2.372874560801656e-24</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02244563054812861</v>
+        <v>1.97215226305253e-29</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/capt_fv_report.xlsx
+++ b/outputs/capt_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.372874560801656e-24</v>
+        <v>2.372874560801657e-24</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/capt_fv_report.xlsx
+++ b/outputs/capt_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.65516714288702</v>
+        <v>12.5889064703791</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.03377777647967</v>
+        <v>11.58070604609571</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17.10507566450418</v>
+        <v>14.94137412704033</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.463949424090978</v>
+        <v>2.440035615145464</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.372874560801657e-24</v>
+        <v>127839.1569760768</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.97215226305253e-29</v>
+        <v>1.080770019070672</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1935.210557192253</v>
+        <v>1607.913201210744</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1086.418089319266</v>
+        <v>957.352754948439</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>290.528184533589</v>
+        <v>289.373184533589</v>
       </c>
     </row>
     <row r="5">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>376.8592576702246</v>
+        <v>372.7012576702245</v>
       </c>
     </row>
     <row r="6">
@@ -733,7 +733,7 @@
         <v/>
       </c>
       <c r="B12" t="n">
-        <v>2010.016088715332</v>
+        <v>1548.340398362997</v>
       </c>
     </row>
     <row r="13">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15.03377777647967</v>
+        <v>11.58070604609571</v>
       </c>
     </row>
     <row r="15">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15.03377777647967</v>
+        <v>11.58070604609571</v>
       </c>
     </row>
     <row r="16">
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>17.48677466252718</v>
+        <v>14.75040947928111</v>
       </c>
       <c r="F11" t="n">
-        <v>13.82716073653219</v>
+        <v>11.66345919906835</v>
       </c>
     </row>
     <row r="12">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>17.10507566450418</v>
+        <v>14.94137412704033</v>
       </c>
     </row>
     <row r="13">
@@ -1064,7 +1064,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
@@ -1110,19 +1110,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.835603218132473</v>
+        <v>7.382594680126135</v>
       </c>
       <c r="C2" t="n">
-        <v>12.37192941325604</v>
+        <v>9.612294807998907</v>
       </c>
       <c r="D2" t="n">
-        <v>14.9082556083796</v>
+        <v>11.84199493587167</v>
       </c>
       <c r="E2" t="n">
-        <v>17.44458180350316</v>
+        <v>14.07169506374445</v>
       </c>
       <c r="F2" t="n">
-        <v>19.98090799862672</v>
+        <v>16.30139519161721</v>
       </c>
     </row>
     <row r="3">
@@ -1132,19 +1132,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10.20905898538619</v>
+        <v>7.756050447379847</v>
       </c>
       <c r="C3" t="n">
-        <v>12.74538518050975</v>
+        <v>9.98575057525262</v>
       </c>
       <c r="D3" t="n">
-        <v>15.28171137563331</v>
+        <v>12.21545070312539</v>
       </c>
       <c r="E3" t="n">
-        <v>17.81803757075687</v>
+        <v>14.44515083099816</v>
       </c>
       <c r="F3" t="n">
-        <v>20.35436376588043</v>
+        <v>16.67485095887093</v>
       </c>
     </row>
     <row r="4">
@@ -1154,19 +1154,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.5825147526399</v>
+        <v>8.12950621463356</v>
       </c>
       <c r="C4" t="n">
-        <v>13.11884094776346</v>
+        <v>10.35920634250633</v>
       </c>
       <c r="D4" t="n">
-        <v>15.65516714288702</v>
+        <v>12.5889064703791</v>
       </c>
       <c r="E4" t="n">
-        <v>18.19149333801059</v>
+        <v>14.81860659825187</v>
       </c>
       <c r="F4" t="n">
-        <v>20.72781953313415</v>
+        <v>17.04830672612464</v>
       </c>
     </row>
     <row r="5">
@@ -1176,19 +1176,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.95597051989361</v>
+        <v>8.502961981887271</v>
       </c>
       <c r="C5" t="n">
-        <v>13.49229671501717</v>
+        <v>10.73266210976004</v>
       </c>
       <c r="D5" t="n">
-        <v>16.02862291014073</v>
+        <v>12.96236223763281</v>
       </c>
       <c r="E5" t="n">
-        <v>18.5649491052643</v>
+        <v>15.19206236550558</v>
       </c>
       <c r="F5" t="n">
-        <v>21.10127530038786</v>
+        <v>17.42176249337835</v>
       </c>
     </row>
     <row r="6">
@@ -1198,19 +1198,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.32942628714732</v>
+        <v>8.876417749140984</v>
       </c>
       <c r="C6" t="n">
-        <v>13.86575248227089</v>
+        <v>11.10611787701376</v>
       </c>
       <c r="D6" t="n">
-        <v>16.40207867739445</v>
+        <v>13.33581800488652</v>
       </c>
       <c r="E6" t="n">
-        <v>18.93840487251801</v>
+        <v>15.5655181327593</v>
       </c>
       <c r="F6" t="n">
-        <v>21.47473106764157</v>
+        <v>17.79521826063207</v>
       </c>
     </row>
   </sheetData>
@@ -1248,7 +1248,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>15.73</v>
+        <v>12.67</v>
       </c>
     </row>
     <row r="3">
@@ -1256,7 +1256,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>15.77</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="4">
@@ -1264,7 +1264,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>15.78</v>
+        <v>12.71</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/capt_fv_report.xlsx
+++ b/outputs/capt_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.79</v>
+        <v>12.73</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12.5889064703791</v>
+        <v>16.12563563694761</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11.58070604609571</v>
+        <v>15.59190826755395</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14.94137412704033</v>
+        <v>17.37099949886615</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.440035615145464</v>
+        <v>2.458279853776168</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>127839.1569760768</v>
+        <v>2.358573720356628e-24</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.080770019070672</v>
+        <v>1.97215226305253e-29</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1607.913201210744</v>
+        <v>1935.210557192253</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>957.352754948439</v>
+        <v>1148.965135975897</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>289.373184533589</v>
+        <v>293.153184533589</v>
       </c>
     </row>
     <row r="5">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>372.7012576702245</v>
+        <v>386.3092576702246</v>
       </c>
     </row>
     <row r="6">
@@ -733,7 +733,7 @@
         <v/>
       </c>
       <c r="B12" t="n">
-        <v>1548.340398362997</v>
+        <v>2084.638135371963</v>
       </c>
     </row>
     <row r="13">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>11.58070604609571</v>
+        <v>15.59190826755395</v>
       </c>
     </row>
     <row r="15">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11.58070604609571</v>
+        <v>15.59190826755395</v>
       </c>
     </row>
     <row r="16">
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>14.75040947928111</v>
+        <v>17.82308015990938</v>
       </c>
       <c r="F11" t="n">
-        <v>11.66345919906835</v>
+        <v>14.09308457089416</v>
       </c>
     </row>
     <row r="12">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>14.94137412704033</v>
+        <v>17.37099949886615</v>
       </c>
     </row>
     <row r="13">
@@ -1064,7 +1064,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
@@ -1110,19 +1110,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.382594680126135</v>
+        <v>10.21197801338094</v>
       </c>
       <c r="C2" t="n">
-        <v>9.612294807998907</v>
+        <v>12.79535105791057</v>
       </c>
       <c r="D2" t="n">
-        <v>11.84199493587167</v>
+        <v>15.37872410244019</v>
       </c>
       <c r="E2" t="n">
-        <v>14.07169506374445</v>
+        <v>17.96209714696981</v>
       </c>
       <c r="F2" t="n">
-        <v>16.30139519161721</v>
+        <v>20.54547019149943</v>
       </c>
     </row>
     <row r="3">
@@ -1132,19 +1132,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.756050447379847</v>
+        <v>10.58543378063466</v>
       </c>
       <c r="C3" t="n">
-        <v>9.98575057525262</v>
+        <v>13.16880682516428</v>
       </c>
       <c r="D3" t="n">
-        <v>12.21545070312539</v>
+        <v>15.7521798696939</v>
       </c>
       <c r="E3" t="n">
-        <v>14.44515083099816</v>
+        <v>18.33555291422352</v>
       </c>
       <c r="F3" t="n">
-        <v>16.67485095887093</v>
+        <v>20.91892595875314</v>
       </c>
     </row>
     <row r="4">
@@ -1154,19 +1154,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.12950621463356</v>
+        <v>10.95888954788837</v>
       </c>
       <c r="C4" t="n">
-        <v>10.35920634250633</v>
+        <v>13.54226259241799</v>
       </c>
       <c r="D4" t="n">
-        <v>12.5889064703791</v>
+        <v>16.12563563694761</v>
       </c>
       <c r="E4" t="n">
-        <v>14.81860659825187</v>
+        <v>18.70900868147724</v>
       </c>
       <c r="F4" t="n">
-        <v>17.04830672612464</v>
+        <v>21.29238172600685</v>
       </c>
     </row>
     <row r="5">
@@ -1176,19 +1176,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.502961981887271</v>
+        <v>11.33234531514208</v>
       </c>
       <c r="C5" t="n">
-        <v>10.73266210976004</v>
+        <v>13.9157183596717</v>
       </c>
       <c r="D5" t="n">
-        <v>12.96236223763281</v>
+        <v>16.49909140420132</v>
       </c>
       <c r="E5" t="n">
-        <v>15.19206236550558</v>
+        <v>19.08246444873095</v>
       </c>
       <c r="F5" t="n">
-        <v>17.42176249337835</v>
+        <v>21.66583749326056</v>
       </c>
     </row>
     <row r="6">
@@ -1198,19 +1198,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.876417749140984</v>
+        <v>11.70580108239579</v>
       </c>
       <c r="C6" t="n">
-        <v>11.10611787701376</v>
+        <v>14.28917412692542</v>
       </c>
       <c r="D6" t="n">
-        <v>13.33581800488652</v>
+        <v>16.87254717145504</v>
       </c>
       <c r="E6" t="n">
-        <v>15.5655181327593</v>
+        <v>19.45592021598466</v>
       </c>
       <c r="F6" t="n">
-        <v>17.79521826063207</v>
+        <v>22.03929326051428</v>
       </c>
     </row>
   </sheetData>
@@ -1248,7 +1248,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>12.67</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="3">
@@ -1256,7 +1256,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>12.7</v>
+        <v>16.24</v>
       </c>
     </row>
     <row r="4">
@@ -1264,7 +1264,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>12.71</v>
+        <v>16.25</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/capt_fv_report.xlsx
+++ b/outputs/capt_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16.12563563694761</v>
+        <v>16.02812497781628</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.59190826755395</v>
+        <v>15.49328077777502</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17.37099949886615</v>
+        <v>17.27609477791257</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.458279853776168</v>
+        <v>2.456916611713618</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.358573720356628e-24</v>
+        <v>2.356262306720752e-24</v>
       </c>
     </row>
     <row r="16">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1935.210557192253</v>
+        <v>1922.375441425454</v>
       </c>
     </row>
     <row r="3">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>293.153184533589</v>
+        <v>294.8018049169445</v>
       </c>
     </row>
     <row r="5">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>386.3092576702246</v>
+        <v>384.3092576702246</v>
       </c>
     </row>
     <row r="6">
@@ -733,7 +733,7 @@
         <v/>
       </c>
       <c r="B12" t="n">
-        <v>2084.638135371963</v>
+        <v>2071.45163998852</v>
       </c>
     </row>
     <row r="13">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15.59190826755395</v>
+        <v>15.49328077777502</v>
       </c>
     </row>
     <row r="15">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15.59190826755395</v>
+        <v>15.49328077777502</v>
       </c>
     </row>
     <row r="16">
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>17.82308015990938</v>
+        <v>17.70305714858063</v>
       </c>
       <c r="F11" t="n">
-        <v>14.09308457089416</v>
+        <v>13.99817984994058</v>
       </c>
     </row>
     <row r="12">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>17.37099949886615</v>
+        <v>17.27609477791257</v>
       </c>
     </row>
     <row r="13">
@@ -1110,19 +1110,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.21197801338094</v>
+        <v>10.13396948607588</v>
       </c>
       <c r="C2" t="n">
-        <v>12.79535105791057</v>
+        <v>12.70759146469237</v>
       </c>
       <c r="D2" t="n">
-        <v>15.37872410244019</v>
+        <v>15.28121344330886</v>
       </c>
       <c r="E2" t="n">
-        <v>17.96209714696981</v>
+        <v>17.85483542192535</v>
       </c>
       <c r="F2" t="n">
-        <v>20.54547019149943</v>
+        <v>20.42845740054183</v>
       </c>
     </row>
     <row r="3">
@@ -1132,19 +1132,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10.58543378063466</v>
+        <v>10.50742525332959</v>
       </c>
       <c r="C3" t="n">
-        <v>13.16880682516428</v>
+        <v>13.08104723194608</v>
       </c>
       <c r="D3" t="n">
-        <v>15.7521798696939</v>
+        <v>15.65466921056257</v>
       </c>
       <c r="E3" t="n">
-        <v>18.33555291422352</v>
+        <v>18.22829118917906</v>
       </c>
       <c r="F3" t="n">
-        <v>20.91892595875314</v>
+        <v>20.80191316779554</v>
       </c>
     </row>
     <row r="4">
@@ -1154,19 +1154,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.95888954788837</v>
+        <v>10.88088102058331</v>
       </c>
       <c r="C4" t="n">
-        <v>13.54226259241799</v>
+        <v>13.45450299919979</v>
       </c>
       <c r="D4" t="n">
-        <v>16.12563563694761</v>
+        <v>16.02812497781628</v>
       </c>
       <c r="E4" t="n">
-        <v>18.70900868147724</v>
+        <v>18.60174695643277</v>
       </c>
       <c r="F4" t="n">
-        <v>21.29238172600685</v>
+        <v>21.17536893504926</v>
       </c>
     </row>
     <row r="5">
@@ -1176,19 +1176,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.33234531514208</v>
+        <v>11.25433678783702</v>
       </c>
       <c r="C5" t="n">
-        <v>13.9157183596717</v>
+        <v>13.82795876645351</v>
       </c>
       <c r="D5" t="n">
-        <v>16.49909140420132</v>
+        <v>16.40158074507</v>
       </c>
       <c r="E5" t="n">
-        <v>19.08246444873095</v>
+        <v>18.97520272368649</v>
       </c>
       <c r="F5" t="n">
-        <v>21.66583749326056</v>
+        <v>21.54882470230297</v>
       </c>
     </row>
     <row r="6">
@@ -1198,19 +1198,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.70580108239579</v>
+        <v>11.62779255509073</v>
       </c>
       <c r="C6" t="n">
-        <v>14.28917412692542</v>
+        <v>14.20141453370722</v>
       </c>
       <c r="D6" t="n">
-        <v>16.87254717145504</v>
+        <v>16.77503651232371</v>
       </c>
       <c r="E6" t="n">
-        <v>19.45592021598466</v>
+        <v>19.3486584909402</v>
       </c>
       <c r="F6" t="n">
-        <v>22.03929326051428</v>
+        <v>21.92228046955668</v>
       </c>
     </row>
   </sheetData>
@@ -1248,7 +1248,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>16.2</v>
+        <v>16.11</v>
       </c>
     </row>
     <row r="3">
@@ -1256,7 +1256,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>16.24</v>
+        <v>16.14</v>
       </c>
     </row>
     <row r="4">
@@ -1264,7 +1264,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>16.25</v>
+        <v>16.15</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/capt_fv_report.xlsx
+++ b/outputs/capt_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.73</v>
+        <v>12.58</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/capt_fv_report.xlsx
+++ b/outputs/capt_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.356262306720752e-24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.97215226305253e-29</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/capt_fv_report.xlsx
+++ b/outputs/capt_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.58</v>
+        <v>12.49</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/capt_fv_report.xlsx
+++ b/outputs/capt_fv_report.xlsx
@@ -1294,7 +1294,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>spot TCE VLCC: $388,300/day is 9.7x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
+          <t>spot TCE VLCC: $285,500/day is 7.1x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
         </is>
       </c>
     </row>

--- a/outputs/capt_fv_report.xlsx
+++ b/outputs/capt_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.49</v>
+        <v>13.28</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/capt_fv_report.xlsx
+++ b/outputs/capt_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13.28</v>
+        <v>13.68</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>6062.924845215614</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.0507456700389616</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/capt_fv_report.xlsx
+++ b/outputs/capt_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13.68</v>
+        <v>13.06</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6062.924845215614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0507456700389616</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/capt_fv_report.xlsx
+++ b/outputs/capt_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13.06</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/capt_fv_report.xlsx
+++ b/outputs/capt_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>13.28</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/capt_fv_report.xlsx
+++ b/outputs/capt_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13.28</v>
+        <v>13.3972</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/capt_fv_report.xlsx
+++ b/outputs/capt_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13.3972</v>
+        <v>12.718</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/capt_fv_report.xlsx
+++ b/outputs/capt_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16.02812497781628</v>
+        <v>16.02854652071104</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.49328077777502</v>
+        <v>15.48793888788854</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17.27609477791257</v>
+        <v>17.28996433063022</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.456916611713618</v>
+        <v>2.456989338164862</v>
       </c>
     </row>
     <row r="12">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>384.3092576702246</v>
+        <v>383.5950469924025</v>
       </c>
     </row>
     <row r="6">
@@ -733,7 +733,7 @@
         <v/>
       </c>
       <c r="B12" t="n">
-        <v>2071.45163998852</v>
+        <v>2070.737429310698</v>
       </c>
     </row>
     <row r="13">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15.49328077777502</v>
+        <v>15.48793888788854</v>
       </c>
     </row>
     <row r="15">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15.49328077777502</v>
+        <v>15.48793888788854</v>
       </c>
     </row>
     <row r="16">
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>17.70305714858063</v>
+        <v>17.72059753504643</v>
       </c>
       <c r="F11" t="n">
-        <v>13.99817984994058</v>
+        <v>14.01204940265823</v>
       </c>
     </row>
     <row r="12">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>17.27609477791257</v>
+        <v>17.28996433063022</v>
       </c>
     </row>
     <row r="13">
@@ -1110,19 +1110,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.13396948607588</v>
+        <v>10.13430672039169</v>
       </c>
       <c r="C2" t="n">
-        <v>12.70759146469237</v>
+        <v>12.70797085329765</v>
       </c>
       <c r="D2" t="n">
-        <v>15.28121344330886</v>
+        <v>15.28163498620362</v>
       </c>
       <c r="E2" t="n">
-        <v>17.85483542192535</v>
+        <v>17.85529911910959</v>
       </c>
       <c r="F2" t="n">
-        <v>20.42845740054183</v>
+        <v>20.42896325201555</v>
       </c>
     </row>
     <row r="3">
@@ -1132,19 +1132,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10.50742525332959</v>
+        <v>10.5077624876454</v>
       </c>
       <c r="C3" t="n">
-        <v>13.08104723194608</v>
+        <v>13.08142662055137</v>
       </c>
       <c r="D3" t="n">
-        <v>15.65466921056257</v>
+        <v>15.65509075345733</v>
       </c>
       <c r="E3" t="n">
-        <v>18.22829118917906</v>
+        <v>18.2287548863633</v>
       </c>
       <c r="F3" t="n">
-        <v>20.80191316779554</v>
+        <v>20.80241901926926</v>
       </c>
     </row>
     <row r="4">
@@ -1154,19 +1154,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.88088102058331</v>
+        <v>10.88121825489912</v>
       </c>
       <c r="C4" t="n">
-        <v>13.45450299919979</v>
+        <v>13.45488238780508</v>
       </c>
       <c r="D4" t="n">
-        <v>16.02812497781628</v>
+        <v>16.02854652071104</v>
       </c>
       <c r="E4" t="n">
-        <v>18.60174695643277</v>
+        <v>18.60221065361701</v>
       </c>
       <c r="F4" t="n">
-        <v>21.17536893504926</v>
+        <v>21.17587478652297</v>
       </c>
     </row>
     <row r="5">
@@ -1176,19 +1176,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.25433678783702</v>
+        <v>11.25467402215283</v>
       </c>
       <c r="C5" t="n">
-        <v>13.82795876645351</v>
+        <v>13.82833815505879</v>
       </c>
       <c r="D5" t="n">
-        <v>16.40158074507</v>
+        <v>16.40200228796476</v>
       </c>
       <c r="E5" t="n">
-        <v>18.97520272368649</v>
+        <v>18.97566642087072</v>
       </c>
       <c r="F5" t="n">
-        <v>21.54882470230297</v>
+        <v>21.54933055377668</v>
       </c>
     </row>
     <row r="6">
@@ -1198,19 +1198,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.62779255509073</v>
+        <v>11.62812978940654</v>
       </c>
       <c r="C6" t="n">
-        <v>14.20141453370722</v>
+        <v>14.2017939223125</v>
       </c>
       <c r="D6" t="n">
-        <v>16.77503651232371</v>
+        <v>16.77545805521847</v>
       </c>
       <c r="E6" t="n">
-        <v>19.3486584909402</v>
+        <v>19.34912218812444</v>
       </c>
       <c r="F6" t="n">
-        <v>21.92228046955668</v>
+        <v>21.9227863210304</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/capt_fv_report.xlsx
+++ b/outputs/capt_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.718</v>
+        <v>12.6039</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/capt_fv_report.xlsx
+++ b/outputs/capt_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.6039</v>
+        <v>13.0112</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/capt_fv_report.xlsx
+++ b/outputs/capt_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13.0112</v>
+        <v>13.5056</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/capt_fv_report.xlsx
+++ b/outputs/capt_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13.5056</v>
+        <v>13.9395</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>19106.83580833613</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.1599102651007897</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/capt_fv_report.xlsx
+++ b/outputs/capt_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16.02854652071104</v>
+        <v>16.04541189566983</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.48793888788854</v>
+        <v>15.48231837430412</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17.28996433063022</v>
+        <v>17.35929677885649</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.456989338164862</v>
+        <v>2.457065885170754</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19106.83580833613</v>
+        <v>18274.30064660041</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1599102651007897</v>
+        <v>0.1529317181730508</v>
       </c>
     </row>
   </sheetData>
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>383.5950469924025</v>
+        <v>382.8435843261648</v>
       </c>
     </row>
     <row r="6">
@@ -733,7 +733,7 @@
         <v/>
       </c>
       <c r="B12" t="n">
-        <v>2070.737429310698</v>
+        <v>2069.98596664446</v>
       </c>
     </row>
     <row r="13">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15.48793888788854</v>
+        <v>15.48231837430412</v>
       </c>
     </row>
     <row r="15">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15.48793888788854</v>
+        <v>15.48231837430412</v>
       </c>
     </row>
     <row r="16">
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>17.72059753504643</v>
+        <v>17.80828009851955</v>
       </c>
       <c r="F11" t="n">
-        <v>14.01204940265823</v>
+        <v>14.0813818508845</v>
       </c>
     </row>
     <row r="12">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>17.28996433063022</v>
+        <v>17.35929677885649</v>
       </c>
     </row>
     <row r="13">
@@ -1110,19 +1110,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.13430672039169</v>
+        <v>10.14779902035872</v>
       </c>
       <c r="C2" t="n">
-        <v>12.70797085329765</v>
+        <v>12.72314969076056</v>
       </c>
       <c r="D2" t="n">
-        <v>15.28163498620362</v>
+        <v>15.2985003611624</v>
       </c>
       <c r="E2" t="n">
-        <v>17.85529911910959</v>
+        <v>17.87385103156425</v>
       </c>
       <c r="F2" t="n">
-        <v>20.42896325201555</v>
+        <v>20.44920170196609</v>
       </c>
     </row>
     <row r="3">
@@ -1132,19 +1132,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10.5077624876454</v>
+        <v>10.52125478761243</v>
       </c>
       <c r="C3" t="n">
-        <v>13.08142662055137</v>
+        <v>13.09660545801427</v>
       </c>
       <c r="D3" t="n">
-        <v>15.65509075345733</v>
+        <v>15.67195612841611</v>
       </c>
       <c r="E3" t="n">
-        <v>18.2287548863633</v>
+        <v>18.24730679881796</v>
       </c>
       <c r="F3" t="n">
-        <v>20.80241901926926</v>
+        <v>20.8226574692198</v>
       </c>
     </row>
     <row r="4">
@@ -1154,19 +1154,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.88121825489912</v>
+        <v>10.89471055486614</v>
       </c>
       <c r="C4" t="n">
-        <v>13.45488238780508</v>
+        <v>13.47006122526798</v>
       </c>
       <c r="D4" t="n">
-        <v>16.02854652071104</v>
+        <v>16.04541189566983</v>
       </c>
       <c r="E4" t="n">
-        <v>18.60221065361701</v>
+        <v>18.62076256607167</v>
       </c>
       <c r="F4" t="n">
-        <v>21.17587478652297</v>
+        <v>21.19611323647351</v>
       </c>
     </row>
     <row r="5">
@@ -1176,19 +1176,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.25467402215283</v>
+        <v>11.26816632211985</v>
       </c>
       <c r="C5" t="n">
-        <v>13.82833815505879</v>
+        <v>13.8435169925217</v>
       </c>
       <c r="D5" t="n">
-        <v>16.40200228796476</v>
+        <v>16.41886766292354</v>
       </c>
       <c r="E5" t="n">
-        <v>18.97566642087072</v>
+        <v>18.99421833332539</v>
       </c>
       <c r="F5" t="n">
-        <v>21.54933055377668</v>
+        <v>21.56956900372722</v>
       </c>
     </row>
     <row r="6">
@@ -1198,19 +1198,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.62812978940654</v>
+        <v>11.64162208937357</v>
       </c>
       <c r="C6" t="n">
-        <v>14.2017939223125</v>
+        <v>14.21697275977541</v>
       </c>
       <c r="D6" t="n">
-        <v>16.77545805521847</v>
+        <v>16.79232343017725</v>
       </c>
       <c r="E6" t="n">
-        <v>19.34912218812444</v>
+        <v>19.3676741005791</v>
       </c>
       <c r="F6" t="n">
-        <v>21.9227863210304</v>
+        <v>21.94302477098094</v>
       </c>
     </row>
   </sheetData>
@@ -1248,7 +1248,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>16.11</v>
+        <v>16.12</v>
       </c>
     </row>
     <row r="3">
@@ -1256,7 +1256,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>16.14</v>
+        <v>16.16</v>
       </c>
     </row>
     <row r="4">
@@ -1264,7 +1264,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>16.15</v>
+        <v>16.17</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/capt_fv_report.xlsx
+++ b/outputs/capt_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16.04541189566983</v>
+        <v>15.1025406478088</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17.35929677885649</v>
+        <v>14.21639261931974</v>
       </c>
     </row>
     <row r="9">
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>111500</v>
+        <v>105700</v>
       </c>
     </row>
     <row r="10">
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>155000</v>
+        <v>142675</v>
       </c>
     </row>
     <row r="11">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.457065885170754</v>
+        <v>2.319104105783838</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18274.30064660041</v>
+        <v>27207.65887715119</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1529317181730508</v>
+        <v>0.2465835334129509</v>
       </c>
     </row>
   </sheetData>
@@ -793,7 +793,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
   </cols>
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>147500</v>
+        <v>179650</v>
       </c>
       <c r="C2" t="n">
-        <v>147500</v>
+        <v>179650</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5467245120605834</v>
+        <v>0.5874500415762902</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2460260304272625</v>
+        <v>0.2643525187093306</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2396902203934713</v>
+        <v>0.2575447539472531</v>
       </c>
     </row>
     <row r="3">
@@ -859,19 +859,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>183500</v>
+        <v>179650</v>
       </c>
       <c r="C3" t="n">
-        <v>183500</v>
+        <v>179650</v>
       </c>
       <c r="D3" t="n">
-        <v>1.043427199981301</v>
+        <v>0.9652836285807779</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4695422399915856</v>
+        <v>0.4343776328613501</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4456697714315523</v>
+        <v>0.4122930034063939</v>
       </c>
     </row>
     <row r="4">
@@ -881,19 +881,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>165500</v>
+        <v>105700</v>
       </c>
       <c r="C4" t="n">
-        <v>165500</v>
+        <v>105700</v>
       </c>
       <c r="D4" t="n">
-        <v>1.108697410433807</v>
+        <v>0.6267730763369485</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4989138346952132</v>
+        <v>0.2820478843516268</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4613529615821943</v>
+        <v>0.2608138273678217</v>
       </c>
     </row>
     <row r="5">
@@ -903,19 +903,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>123500</v>
+        <v>105700</v>
       </c>
       <c r="C5" t="n">
-        <v>123500</v>
+        <v>105700</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9026868172213912</v>
+        <v>0.7256192975878833</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4062090677496261</v>
+        <v>0.3265286839145475</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3659541150897532</v>
+        <v>0.2941699855086014</v>
       </c>
     </row>
     <row r="6">
@@ -925,19 +925,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>111500</v>
+        <v>48850</v>
       </c>
       <c r="C6" t="n">
-        <v>111500</v>
+        <v>48850</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8307552680441287</v>
+        <v>0.3104440320493643</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3738398706198579</v>
+        <v>0.1396998144222139</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3281193890470323</v>
+        <v>0.1226145774183931</v>
       </c>
     </row>
     <row r="7">
@@ -947,19 +947,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>135500</v>
+        <v>48850</v>
       </c>
       <c r="C7" t="n">
-        <v>135500</v>
+        <v>48850</v>
       </c>
       <c r="D7" t="n">
-        <v>1.210069758601346</v>
+        <v>0.3505238821615557</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5445313913706058</v>
+        <v>0.1577357469727001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4656273189708502</v>
+        <v>0.1348794103199381</v>
       </c>
     </row>
     <row r="8">
@@ -969,19 +969,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>147500</v>
+        <v>48850</v>
       </c>
       <c r="C8" t="n">
-        <v>147500</v>
+        <v>48850</v>
       </c>
       <c r="D8" t="n">
-        <v>1.489150533096485</v>
+        <v>0.404895951551982</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6701177398934182</v>
+        <v>0.1822031781983919</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5582592171144143</v>
+        <v>0.1517891522062531</v>
       </c>
     </row>
     <row r="9">
@@ -991,19 +991,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>105500</v>
+        <v>48850</v>
       </c>
       <c r="C9" t="n">
-        <v>105500</v>
+        <v>48850</v>
       </c>
       <c r="D9" t="n">
-        <v>1.131456416230366</v>
+        <v>0.4592680209424084</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5091553873036649</v>
+        <v>0.2066706094240838</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4132419343427196</v>
+        <v>0.1677385029008066</v>
       </c>
     </row>
     <row r="10">
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.277914927971987</v>
+        <v>1.801843213075461</v>
       </c>
     </row>
     <row r="11">
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>17.80828009851955</v>
+        <v>15.70028960683435</v>
       </c>
       <c r="F11" t="n">
-        <v>14.0813818508845</v>
+        <v>12.41454940624428</v>
       </c>
     </row>
     <row r="12">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>17.35929677885649</v>
+        <v>14.21639261931974</v>
       </c>
     </row>
     <row r="13">
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>155000</v>
+        <v>142675</v>
       </c>
     </row>
   </sheetData>
@@ -1110,19 +1110,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.14779902035872</v>
+        <v>9.487789146855999</v>
       </c>
       <c r="C2" t="n">
-        <v>12.72314969076056</v>
+        <v>12.06313981725784</v>
       </c>
       <c r="D2" t="n">
-        <v>15.2985003611624</v>
+        <v>14.63849048765968</v>
       </c>
       <c r="E2" t="n">
-        <v>17.87385103156425</v>
+        <v>17.21384115806153</v>
       </c>
       <c r="F2" t="n">
-        <v>20.44920170196609</v>
+        <v>19.78919182846337</v>
       </c>
     </row>
     <row r="3">
@@ -1132,19 +1132,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10.52125478761243</v>
+        <v>9.719814226930557</v>
       </c>
       <c r="C3" t="n">
-        <v>13.09660545801427</v>
+        <v>12.2951648973324</v>
       </c>
       <c r="D3" t="n">
-        <v>15.67195612841611</v>
+        <v>14.87051556773424</v>
       </c>
       <c r="E3" t="n">
-        <v>18.24730679881796</v>
+        <v>17.44586623813609</v>
       </c>
       <c r="F3" t="n">
-        <v>20.8226574692198</v>
+        <v>20.02121690853793</v>
       </c>
     </row>
     <row r="4">
@@ -1154,19 +1154,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.89471055486614</v>
+        <v>9.951839307005116</v>
       </c>
       <c r="C4" t="n">
-        <v>13.47006122526798</v>
+        <v>12.52718997740696</v>
       </c>
       <c r="D4" t="n">
-        <v>16.04541189566983</v>
+        <v>15.1025406478088</v>
       </c>
       <c r="E4" t="n">
-        <v>18.62076256607167</v>
+        <v>17.67789131821065</v>
       </c>
       <c r="F4" t="n">
-        <v>21.19611323647351</v>
+        <v>20.25324198861249</v>
       </c>
     </row>
     <row r="5">
@@ -1176,19 +1176,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.26816632211985</v>
+        <v>10.18386438707968</v>
       </c>
       <c r="C5" t="n">
-        <v>13.8435169925217</v>
+        <v>12.75921505748152</v>
       </c>
       <c r="D5" t="n">
-        <v>16.41886766292354</v>
+        <v>15.33456572788336</v>
       </c>
       <c r="E5" t="n">
-        <v>18.99421833332539</v>
+        <v>17.9099163982852</v>
       </c>
       <c r="F5" t="n">
-        <v>21.56956900372722</v>
+        <v>20.48526706868704</v>
       </c>
     </row>
     <row r="6">
@@ -1198,19 +1198,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.64162208937357</v>
+        <v>10.41588946715423</v>
       </c>
       <c r="C6" t="n">
-        <v>14.21697275977541</v>
+        <v>12.99124013755608</v>
       </c>
       <c r="D6" t="n">
-        <v>16.79232343017725</v>
+        <v>15.56659080795792</v>
       </c>
       <c r="E6" t="n">
-        <v>19.3676741005791</v>
+        <v>18.14194147835977</v>
       </c>
       <c r="F6" t="n">
-        <v>21.94302477098094</v>
+        <v>20.7172921487616</v>
       </c>
     </row>
   </sheetData>
@@ -1248,7 +1248,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>16.12</v>
+        <v>15.16</v>
       </c>
     </row>
     <row r="3">
@@ -1256,7 +1256,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>16.16</v>
+        <v>15.18</v>
       </c>
     </row>
     <row r="4">
@@ -1264,7 +1264,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>16.17</v>
+        <v>15.19</v>
       </c>
     </row>
   </sheetData>
@@ -1294,7 +1294,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>spot TCE VLCC: $285,500/day is 7.1x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
+          <t>spot TCE VLCC: $488,900/day is 12.2x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
         </is>
       </c>
     </row>

--- a/outputs/capt_fv_report.xlsx
+++ b/outputs/capt_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13.9395</v>
+        <v>14.306</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27207.65887715119</v>
+        <v>53519.79630122242</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2465835334129509</v>
+        <v>0.4850509387479728</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/capt_fv_report.xlsx
+++ b/outputs/capt_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14.306</v>
+        <v>14.6837</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>53519.79630122242</v>
+        <v>80461.83248322531</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4850509387479728</v>
+        <v>0.7292271285882892</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/capt_fv_report.xlsx
+++ b/outputs/capt_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14.6837</v>
+        <v>16.5334</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>80461.83248322531</v>
+        <v>212404.3379792557</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7292271285882892</v>
+        <v>1.925024582513713</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/capt_fv_report.xlsx
+++ b/outputs/capt_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.5334</v>
+        <v>16.4629</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>212404.3379792557</v>
+        <v>207375.4432193109</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.925024582513713</v>
+        <v>1.879447613004203</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/capt_fv_report.xlsx
+++ b/outputs/capt_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.4629</v>
+        <v>16.4636</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>207375.4432193109</v>
+        <v>207425.3755077074</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.879447613004203</v>
+        <v>1.879900150290112</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/capt_fv_report.xlsx
+++ b/outputs/capt_fv_report.xlsx
@@ -461,7 +461,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-Q1</t>
+          <t>2026-Q2</t>
         </is>
       </c>
     </row>
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.1025406478088</v>
+        <v>16.9479358664871</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.48231837430412</v>
+        <v>17.31548984010943</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14.21639261931974</v>
+        <v>16.09030992803501</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.319104105783838</v>
+        <v>2.360069842488456</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>207425.3755077074</v>
+        <v>63532.37063167423</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.879900150290112</v>
+        <v>0.5547851025773256</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1922.375441425454</v>
+        <v>2442.731935364646</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1148.965135975897</v>
+        <v>1145.526603002084</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>294.8018049169445</v>
+        <v>287.3471461594781</v>
       </c>
     </row>
     <row r="5">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>382.8435843261648</v>
+        <v>374.6000512631759</v>
       </c>
     </row>
     <row r="6">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>405</v>
+        <v>350.205</v>
       </c>
     </row>
     <row r="7">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>41.978</v>
       </c>
     </row>
     <row r="8">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-217</v>
+        <v>-520.836</v>
       </c>
     </row>
     <row r="9">
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-1880</v>
+        <v>-1806.6</v>
       </c>
     </row>
     <row r="11">
@@ -733,7 +733,7 @@
         <v/>
       </c>
       <c r="B12" t="n">
-        <v>2069.98596664446</v>
+        <v>2314.952735789385</v>
       </c>
     </row>
     <row r="13">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>133700000</v>
+        <v>133692593</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15.48231837430412</v>
+        <v>17.31548984010943</v>
       </c>
     </row>
     <row r="15">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15.48231837430412</v>
+        <v>17.31548984010943</v>
       </c>
     </row>
     <row r="16">
@@ -793,7 +793,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
   </cols>
@@ -840,16 +840,16 @@
         <v>179650</v>
       </c>
       <c r="C2" t="n">
-        <v>179650</v>
+        <v>97076</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5874500415762902</v>
+        <v>0.6406685721844739</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2643525187093306</v>
+        <v>0.2883008574830133</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2575447539472531</v>
+        <v>0.2808763607237912</v>
       </c>
     </row>
     <row r="3">
@@ -862,16 +862,16 @@
         <v>179650</v>
       </c>
       <c r="C3" t="n">
-        <v>179650</v>
+        <v>97076</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9652836285807779</v>
+        <v>0.8108775925619155</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4343776328613501</v>
+        <v>0.364894916652862</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4122930034063939</v>
+        <v>0.3463429277505057</v>
       </c>
     </row>
     <row r="4">
@@ -884,16 +884,16 @@
         <v>105700</v>
       </c>
       <c r="C4" t="n">
-        <v>105700</v>
+        <v>97076</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6267730763369485</v>
+        <v>0.5003963147226115</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2820478843516268</v>
+        <v>0.2251783416251752</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2608138273678217</v>
+        <v>0.2082257247013527</v>
       </c>
     </row>
     <row r="5">
@@ -906,16 +906,16 @@
         <v>105700</v>
       </c>
       <c r="C5" t="n">
-        <v>105700</v>
+        <v>97076</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7256192975878833</v>
+        <v>0.6314917744689864</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3265286839145475</v>
+        <v>0.2841712985110439</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2941699855086014</v>
+        <v>0.2560101788387782</v>
       </c>
     </row>
     <row r="6">
@@ -928,16 +928,16 @@
         <v>48850</v>
       </c>
       <c r="C6" t="n">
-        <v>48850</v>
+        <v>97076</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3104440320493643</v>
+        <v>0.5095754389219228</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1396998144222139</v>
+        <v>0.2293089475148653</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1226145774183931</v>
+        <v>0.2012645457982857</v>
       </c>
     </row>
     <row r="7">
@@ -950,16 +950,16 @@
         <v>48850</v>
       </c>
       <c r="C7" t="n">
-        <v>48850</v>
+        <v>97076</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3505238821615557</v>
+        <v>0.7056381476443875</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1577357469727001</v>
+        <v>0.3175371664399744</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1348794103199381</v>
+        <v>0.2715251715991835</v>
       </c>
     </row>
     <row r="8">
@@ -972,16 +972,16 @@
         <v>48850</v>
       </c>
       <c r="C8" t="n">
-        <v>48850</v>
+        <v>97076</v>
       </c>
       <c r="D8" t="n">
-        <v>0.404895951551982</v>
+        <v>0.8539040016968253</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1822031781983919</v>
+        <v>0.3842568007635714</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1517891522062531</v>
+        <v>0.3201152394492337</v>
       </c>
     </row>
     <row r="9">
@@ -994,16 +994,16 @@
         <v>48850</v>
       </c>
       <c r="C9" t="n">
-        <v>48850</v>
+        <v>97076</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4592680209424084</v>
+        <v>1.025140539701926</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2066706094240838</v>
+        <v>0.4613132428658669</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1677385029008066</v>
+        <v>0.3744121766625005</v>
       </c>
     </row>
     <row r="10">
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.801843213075461</v>
+        <v>2.258772325523631</v>
       </c>
     </row>
     <row r="11">
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>15.70028960683435</v>
+        <v>17.49230994707074</v>
       </c>
       <c r="F11" t="n">
-        <v>12.41454940624428</v>
+        <v>13.83153760251138</v>
       </c>
     </row>
     <row r="12">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>14.21639261931974</v>
+        <v>16.09030992803501</v>
       </c>
     </row>
     <row r="13">
@@ -1110,19 +1110,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.487789146855999</v>
+        <v>10.80235147559025</v>
       </c>
       <c r="C2" t="n">
-        <v>12.06313981725784</v>
+        <v>13.7119631925919</v>
       </c>
       <c r="D2" t="n">
-        <v>14.63849048765968</v>
+        <v>16.62157490959354</v>
       </c>
       <c r="E2" t="n">
-        <v>17.21384115806153</v>
+        <v>19.53118662659519</v>
       </c>
       <c r="F2" t="n">
-        <v>19.78919182846337</v>
+        <v>22.44079834359683</v>
       </c>
     </row>
     <row r="3">
@@ -1132,19 +1132,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.719814226930557</v>
+        <v>10.96553195403703</v>
       </c>
       <c r="C3" t="n">
-        <v>12.2951648973324</v>
+        <v>13.87514367103868</v>
       </c>
       <c r="D3" t="n">
-        <v>14.87051556773424</v>
+        <v>16.78475538804032</v>
       </c>
       <c r="E3" t="n">
-        <v>17.44586623813609</v>
+        <v>19.69436710504197</v>
       </c>
       <c r="F3" t="n">
-        <v>20.02121690853793</v>
+        <v>22.60397882204362</v>
       </c>
     </row>
     <row r="4">
@@ -1154,19 +1154,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.951839307005116</v>
+        <v>11.12871243248381</v>
       </c>
       <c r="C4" t="n">
-        <v>12.52718997740696</v>
+        <v>14.03832414948546</v>
       </c>
       <c r="D4" t="n">
-        <v>15.1025406478088</v>
+        <v>16.9479358664871</v>
       </c>
       <c r="E4" t="n">
-        <v>17.67789131821065</v>
+        <v>19.85754758348875</v>
       </c>
       <c r="F4" t="n">
-        <v>20.25324198861249</v>
+        <v>22.76715930049039</v>
       </c>
     </row>
     <row r="5">
@@ -1176,19 +1176,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.18386438707968</v>
+        <v>11.29189291093059</v>
       </c>
       <c r="C5" t="n">
-        <v>12.75921505748152</v>
+        <v>14.20150462793224</v>
       </c>
       <c r="D5" t="n">
-        <v>15.33456572788336</v>
+        <v>17.11111634493388</v>
       </c>
       <c r="E5" t="n">
-        <v>17.9099163982852</v>
+        <v>20.02072806193553</v>
       </c>
       <c r="F5" t="n">
-        <v>20.48526706868704</v>
+        <v>22.93033977893717</v>
       </c>
     </row>
     <row r="6">
@@ -1198,19 +1198,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.41588946715423</v>
+        <v>11.45507338937737</v>
       </c>
       <c r="C6" t="n">
-        <v>12.99124013755608</v>
+        <v>14.36468510637902</v>
       </c>
       <c r="D6" t="n">
-        <v>15.56659080795792</v>
+        <v>17.27429682338066</v>
       </c>
       <c r="E6" t="n">
-        <v>18.14194147835977</v>
+        <v>20.18390854038231</v>
       </c>
       <c r="F6" t="n">
-        <v>20.7172921487616</v>
+        <v>23.09352025738395</v>
       </c>
     </row>
   </sheetData>
@@ -1248,7 +1248,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>15.16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -1256,7 +1256,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>15.18</v>
+        <v>17.03</v>
       </c>
     </row>
     <row r="4">
@@ -1264,7 +1264,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>15.19</v>
+        <v>17.04</v>
       </c>
     </row>
   </sheetData>
